--- a/09. Other tools/03.Dictionary/en_phrasal_verbs.xlsx
+++ b/09. Other tools/03.Dictionary/en_phrasal_verbs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B151"/>
+  <dimension ref="A1:B201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,1798 +431,2398 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ask for</t>
+          <t>Act up</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Искам / Моля за</t>
+          <t>Не работи правилно (уред) / Държа се лошо</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Back up</t>
+          <t>Add up</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Подкрепям (някого) / Правя резервно копие</t>
+          <t>Сборувам се / Има логика</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Blow up</t>
+          <t>Add up to</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Взривявам / Избухвам</t>
+          <t>Възлиза на</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Break down</t>
+          <t>Ask for</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Развалям се (за кола, уред) / Сривам се емоционално</t>
+          <t>Искам / Моля за</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Break in</t>
+          <t>Back down</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Нахлувам с взлом / Прекъсвам разговор</t>
+          <t>Отстъпвам от позиция</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Break out</t>
+          <t>Back off</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Избухвам (война, епидемия, пожар) / Бягам от затвор</t>
+          <t>Отдръпвам се / Оставям на мира</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Break up</t>
+          <t>Back up</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Разделям се (късам връзка) / Разпадам се</t>
+          <t>Подкрепям (някого) / Правя резервно копие</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bring about</t>
+          <t>Bank on</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Предизвиквам / Довеждам до</t>
+          <t>Разчитам на</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bring up</t>
+          <t>Bear with</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Отглеждам (дете) / Повдигам въпрос/тема</t>
+          <t>Имам търпение с</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Call back</t>
+          <t>Blow up</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Обаждам се обратно</t>
+          <t>Взривявам / Избухвам</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Call off</t>
+          <t>Bottle up</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Отменям (събитие, среща)</t>
+          <t>Потискам (чувства)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Call on</t>
+          <t>Bounce back</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Посещавам някого / Призовавам</t>
+          <t>Възстановявам се бързо</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Calm down</t>
+          <t>Branch out</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Успокоявам се</t>
+          <t>Разширявам дейност</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Carry on</t>
+          <t>Break away</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Продължавам (да правя нещо)</t>
+          <t>Отделям се / Освобождавам се</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Carry out</t>
+          <t>Break down</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Изпълнявам (план, поръчка, изследване)</t>
+          <t>Развалям се (за кола, уред) / Сривам се емоционално</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Catch up (with)</t>
+          <t>Break in</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Настигам (някого) / Наваксвам</t>
+          <t>Нахлувам с взлом / Прекъсвам разговор</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Check in</t>
+          <t>Break off</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Регистрирам се (в хотел, летище)</t>
+          <t>Прекъсвам внезапно (връзка, разговор)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Check out</t>
+          <t>Break out</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Плащам и напускам хотел / Проверявам / Разглеждам</t>
+          <t>Избухвам (война, епидемия, пожар) / Бягам от затвор</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Clean up</t>
+          <t>Break up</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Почиствам основно</t>
+          <t>Разделям се (късам връзка) / Разпадам се</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Close down</t>
+          <t>Brighten up</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Затварям завинаги (бизнес, фабрика)</t>
+          <t>Разведрявам се / Оживявам</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Come across</t>
+          <t>Bring about</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Натъквам се на / Попадам случайно на</t>
+          <t>Предизвиквам / Довеждам до</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Come along</t>
+          <t>Bring down</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Придружавам / Напредвам</t>
+          <t>Свалям (правителство, цена)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Come back</t>
+          <t>Bring forward</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Връщам се</t>
+          <t>Изнасям по-рано (среща, дата)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Come down with</t>
+          <t>Bring in</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Разболявам се от (грип, настинка)</t>
+          <t>Въвеждам (закон) / Наемам</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Come out</t>
+          <t>Bring out</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Излизам (книга, филм) / Разкривам се</t>
+          <t>Пускам на пазара (продукт)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Come up with</t>
+          <t>Bring up</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Измислям (идея, план, решение)</t>
+          <t>Отглеждам (дете) / Повдигам въпрос/тема</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Count on</t>
+          <t>Brush up on</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Разчитам на</t>
+          <t>Опреснявам знания</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cut back (on)</t>
+          <t>Build up</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Намалявам разходите / Ограничавам (ядене, цигари)</t>
+          <t>Натрупвам постепенно</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cut down (on)</t>
+          <t>Burn out</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Намалявам количеството на</t>
+          <t>Изгарям от преумора</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cut off</t>
+          <t>Butt in</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Прекъсвам (телефонна връзка) / Изолирам / Спирам кран/ток</t>
+          <t>Намесвам се неканен</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cut out</t>
+          <t>Call back</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Изрязвам / Спирам да правя нещо (напр. ям захар)</t>
+          <t>Обаждам се обратно</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deal with</t>
+          <t>Call in</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Справям се с / Занимавам се с</t>
+          <t>Извиквам специалист / Отбивам се</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Die out</t>
+          <t>Call off</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Изчезвам / Измирам (за видове, традиции)</t>
+          <t>Отменям (събитие, среща)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Do without</t>
+          <t>Call on</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Справям се без / Минавам без</t>
+          <t>Посещавам някого / Призовавам</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Draw up</t>
+          <t>Call up</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Съставям (договор, документ) / Спирам (за превозно средство)</t>
+          <t>Обаждам се по телефона / Мобилизирам</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Drop by / in</t>
+          <t>Calm down</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Набивам се / Отбивам се за кратко</t>
+          <t>Успокоявам се</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Drop off</t>
+          <t>Carry away (get carried away)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Оставям някого/нещо по пътя / Заспивам лесно</t>
+          <t>Увличам се</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Drop out</t>
+          <t>Carry on</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Отпадам (от училище, състезание)</t>
+          <t>Продължавам (да правя нещо)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>End up</t>
+          <t>Carry out</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Озовавам се (на дадено място или в ситуация)</t>
+          <t>Изпълнявам (план, поръчка, изследване)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fall apart</t>
+          <t>Cash in on</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Разпадам се (на части) / Сривам се емоционално</t>
+          <t>Извличам полза от</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fall behind</t>
+          <t>Catch on</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Изоставам (с материал, работа, плащания)</t>
+          <t>Разбирам / Става популярно</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fall out (with)</t>
+          <t>Catch up (with)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Скарам се с някого</t>
+          <t>Настигам (някого) / Наваксвам</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Figure out</t>
+          <t>Chase up</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Проумявам / Разбирам / Разгадавам</t>
+          <t>Издирвам / Напомням за просрочено</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fill in</t>
+          <t>Check in</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Попълвам (формуляр) / Замествам колега</t>
+          <t>Регистрирам се (в хотел, летище)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fill out</t>
+          <t>Check out</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Попълвам (документ, бланка)</t>
+          <t>Плащам и напускам хотел / Проверявам / Разглеждам</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Find out</t>
+          <t>Cheer up</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Научавам / Разкривам / Разбирам тайна</t>
+          <t>Разведрявам се</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Get along (with)</t>
+          <t>Chip in</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Разбирам се добре с някого</t>
+          <t>Допринасям (пари, идея)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Get away (with)</t>
+          <t>Clean up</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Избягвам наказание / Измъквам се безнаказано</t>
+          <t>Почиствам основно</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Get back</t>
+          <t>Clear up</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Връщам се / Получавам обратно</t>
+          <t>Изяснявам се / Прояснява се (времето)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Get by</t>
+          <t>Close down</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Преживявам / Справям се криво-ляво (финансово)</t>
+          <t>Затварям завинаги (бизнес, фабрика)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Get in / into</t>
+          <t>Close in</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Влизам / Качвам се (в кола) / Пристигам</t>
+          <t>Приближавам заплашително</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Get off</t>
+          <t>Come across</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Слизам от (автобус, влак) / Отървавам се с леко наказание</t>
+          <t>Натъквам се на / Попадам случайно на</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Get on</t>
+          <t>Come along</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Качвам се на (автобус, влак, велосипед) / Напредвам</t>
+          <t>Придружавам / Напредвам</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Get on with</t>
+          <t>Come apart</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Продължавам работа по / Разбирам се с някого</t>
+          <t>Разпада се</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Get out (of)</t>
+          <t>Come back</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Излизам от (кола, сграда) / Избягвам задължение</t>
+          <t>Връщам се</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Get over</t>
+          <t>Come down with</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Преодолявам (трудност, раздяла) / Възстановявам се от болест</t>
+          <t>Разболявам се от (грип, настинка)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Get rid of</t>
+          <t>Come out</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Отървавам се от / Изхвърлям</t>
+          <t>Излизам (книга, филм) / Разкривам се</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Get together</t>
+          <t>Come round / around</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Събираме се / Срещаме се</t>
+          <t>Идвам на себе си / Съгласявам се накрая</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Get up</t>
+          <t>Come up</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ставам (от леглото, от стол)</t>
+          <t>Изниквам (въпрос, тема)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Give away</t>
+          <t>Come up with</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Подарявам / Издавам тайна</t>
+          <t>Измислям (идея, план, решение)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Give back</t>
+          <t>Cool down</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Връщам (нещо на някого)</t>
+          <t>Охлаждам се / Успокоявам се</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Give in</t>
+          <t>Count on</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Предавам се / Отстъпвам пред натиск</t>
+          <t>Разчитам на</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Give out</t>
+          <t>Cover up</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Раздавам / Изхабявам се (спирам да работя)</t>
+          <t>Прикривам (скандал)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Give up</t>
+          <t>Crack down on</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Отказвам се / Спирам да правя нещо (напр. пушене)</t>
+          <t>Взимам строги мерки срещу</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Go ahead</t>
+          <t>Cross out</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Давай напред / Продължавай (с разрешение)</t>
+          <t>Задрасквам</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Go away</t>
+          <t>Curl up</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Отивам си / Напускам</t>
+          <t>Свивам се на кълбо</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Go by</t>
+          <t>Cut back (on)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Минавам (за време) / Ръководя се от</t>
+          <t>Намалявам разходите / Ограничавам (ядене, цигари)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Go down</t>
+          <t>Cut down (on)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Слизам / Намалявам (цена, температура)</t>
+          <t>Намалявам количеството на</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Go off</t>
+          <t>Cut off</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Изваждам от строй / Избухвам (аларма, бомба) / Развалям се (храна)</t>
+          <t>Прекъсвам (телефонна връзка) / Изолирам / Спирам кран/ток</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Go on</t>
+          <t>Cut out</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Продължавам / Случва се</t>
+          <t>Изрязвам / Спирам да правя нещо (напр. ям захар)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Go out</t>
+          <t>Dawn on</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Излизам (на среща, разходка) / Гасна (за огън, лампа)</t>
+          <t>Осъзнавам внезапно</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Go over</t>
+          <t>Deal with</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Преглеждам внимателно / Повтарям</t>
+          <t>Справям се с / Занимавам се с</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Go through</t>
+          <t>Delve into</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Преминавам през (труден период) / Изследвам подробно</t>
+          <t>Задълбочавам се в</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Go up</t>
+          <t>Die out</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Вдигам се / Нараствам (цена, ниво)</t>
+          <t>Изчезвам / Измирам (за видове, традиции)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Grow up</t>
+          <t>Dig up</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Пораствам / Раста</t>
+          <t>Изравям (факти, информация)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Hand in</t>
+          <t>Dive into</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Предавам (документ, домашна работа)</t>
+          <t>Захващам се енергично с</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Hand out</t>
+          <t>Do without</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Раздавам (брошури, листовки)</t>
+          <t>Справям се без / Минавам без</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Hang on</t>
+          <t>Draw up</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Чакам за кратко (на телефон) / Държа се здраво</t>
+          <t>Съставям (договор, документ) / Спирам (за превозно средство)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Hang out</t>
+          <t>Dress up</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Прекарвам свободното време (вися с приятели)</t>
+          <t>Обличам се официално</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Hang up</t>
+          <t>Drift apart</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Затварям телефона / Закачам дреха</t>
+          <t>Отдалечаваме се (за връзка)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Hold on</t>
+          <t>Drive away</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Изчаквам малко / Държа се здраво</t>
+          <t>Прогонвам</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Hold up</t>
+          <t>Drop by / in</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Забавям (трафик, процес) / Обирам с оръжие</t>
+          <t>Набивам се / Отбивам се за кратко</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Keep up (with)</t>
+          <t>Drop off</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Държа темпото / В крак съм с</t>
+          <t>Оставям някого/нещо по пътя / Заспивам лесно</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Keep on</t>
+          <t>Drop out</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Продължавам да правя нещо</t>
+          <t>Отпадам (от училище, състезание)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Let down</t>
+          <t>Dwell on</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Разочаровам някого / Предавам доверие</t>
+          <t>Мисля прекалено много за</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Let in</t>
+          <t>Ease off</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Пускам да влезе</t>
+          <t>Намалявам интензивността</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Let out</t>
+          <t>Eat out</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Пускам да излезе / Изпускам звук</t>
+          <t>Храня се навън (в ресторант)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Log in / on</t>
+          <t>End up</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Влизам в профил (интернет)</t>
+          <t>Озовавам се (на дадено място или в ситуация)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Log out / off</t>
+          <t>Face up to</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Излизам от профил (интернет)</t>
+          <t>Изправям се пред (проблем)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Look after</t>
+          <t>Fall apart</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Грижа се за (дете, домашен любимец)</t>
+          <t>Разпадам се (на части) / Сривам се емоционално</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Look down on</t>
+          <t>Fall behind</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Гледам отвисоко / Презирам</t>
+          <t>Изоставам (с материал, работа, плащания)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Look for</t>
+          <t>Fall out (with)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Търся</t>
+          <t>Скарам се с някого</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Look forward to</t>
+          <t>Figure out</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Очаквам с нетърпение</t>
+          <t>Проумявам / Разбирам / Разгадавам</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Look into</t>
+          <t>Fill in</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Разследвам / Проучвам</t>
+          <t>Попълвам (формуляр) / Замествам колега</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Look out</t>
+          <t>Fill out</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Внимавам / Пазя се</t>
+          <t>Попълвам (документ, бланка)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Look over</t>
+          <t>Find out</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Преглеждам бързо</t>
+          <t>Научавам / Разкривам / Разбирам тайна</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Look up</t>
+          <t>Get along (with)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Търся информация (в речник, каталог) / Подобрявам се</t>
+          <t>Разбирам се добре с някого</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Look up to</t>
+          <t>Get away (with)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Уважавам / Възхищавам се на някого</t>
+          <t>Избягвам наказание / Измъквам се безнаказано</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Make out</t>
+          <t>Get back</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Разбирам / Разчитам (труден текст) / Справям се</t>
+          <t>Връщам се / Получавам обратно</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Make up</t>
+          <t>Get by</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Измислям си (история) / Гримирам се / Помирявам се</t>
+          <t>Преживявам / Справям се криво-ляво (финансово)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Make up for</t>
+          <t>Get in / into</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Компенсирам за</t>
+          <t>Влизам / Качвам се (в кола) / Пристигам</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Mix up</t>
+          <t>Get off</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Обърквам (неща/хора едно с друго)</t>
+          <t>Слизам от (автобус, влак) / Отървавам се с леко наказание</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Pass away</t>
+          <t>Get on</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Почивам (умирам - учтиво)</t>
+          <t>Качвам се на (автобус, влак, велосипед) / Напредвам</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Pass out</t>
+          <t>Get on with</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Припадам / Губя съзнание</t>
+          <t>Продължавам работа по / Разбирам се с някого</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Pay back</t>
+          <t>Get out (of)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Връщам заем (на някого)</t>
+          <t>Излизам от (кола, сграда) / Избягвам задължение</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Pay off</t>
+          <t>Get over</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Изплащам напълно дълг / Давам добър резултат (усилие)</t>
+          <t>Преодолявам (трудност, раздяла) / Възстановявам се от болест</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Pick up</t>
+          <t>Get rid of</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Вдигам / Взимам някого с кола / Уча лесно</t>
+          <t>Отървавам се от / Изхвърлям</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Point out</t>
+          <t>Get together</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Посочвам / Обръщам внимание на</t>
+          <t>Събираме се / Срещаме се</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Pull over</t>
+          <t>Get up</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Спирам край пътя (за превозно средство)</t>
+          <t>Ставам (от леглото, от стол)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Put away</t>
+          <t>Give away</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Прибирам на мястото му / Спестявам пари</t>
+          <t>Подарявам / Издавам тайна</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Put off</t>
+          <t>Give back</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Отлагам (среща, ангажимент) / Отблъсквам (някого)</t>
+          <t>Връщам (нещо на някого)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Put on</t>
+          <t>Give in</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Обличам (дреха) / Обувам / Надебелявам / Включвам</t>
+          <t>Предавам се / Отстъпвам пред натиск</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Put out</t>
+          <t>Give out</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Гася (пожар, цигара) / Безпокоя (някого)</t>
+          <t>Раздавам / Изхабявам се (спирам да работя)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Put up with</t>
+          <t>Give up</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Измъчвам се / Толерирам / Търпя (неприятно нещо)</t>
+          <t>Отказвам се / Спирам да правя нещо (напр. пушене)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Run into</t>
+          <t>Go ahead</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Сблъсквам се / Срещам случайно някого</t>
+          <t>Давай напред / Продължавай (с разрешение)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Run out of</t>
+          <t>Go away</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Свършвам (напр. нямаме бензин, мляко)</t>
+          <t>Отивам си / Напускам</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Run over</t>
+          <t>Go by</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Прегазвам с кола / Преглеждам бързо</t>
+          <t>Минавам (за време) / Ръководя се от</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Save up</t>
+          <t>Go down</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Спестявам (пари за нещо специално)</t>
+          <t>Слизам / Намалявам (цена, температура)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>See off</t>
+          <t>Go off</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Изпращам някого (на гара, летище)</t>
+          <t>Изваждам от строй / Избухвам (аларма, бомба) / Развалям се (храна)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Set off / out</t>
+          <t>Go on</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Тръгвам на път / Задействам аларма</t>
+          <t>Продължавам / Случва се</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Set up</t>
+          <t>Go out</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Основавам (фирма) / Организирам / Нагласям капан</t>
+          <t>Излизам (на среща, разходка) / Гасна (за огън, лампа)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Show off</t>
+          <t>Go over</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Фукам се / Перча се</t>
+          <t>Преглеждам внимателно / Повтарям</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Show up</t>
+          <t>Go through</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Появявам се / Идвам на среща</t>
+          <t>Преминавам през (труден период) / Изследвам подробно</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Slow down</t>
+          <t>Go up</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Намалявам скоростта</t>
+          <t>Вдигам се / Нараствам (цена, ниво)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sort out</t>
+          <t>Grow up</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Решавам проблем / Подреждам</t>
+          <t>Пораствам / Раста</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Stand by</t>
+          <t>Hand in</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Подкрепям (някого) / Изчаквам готовност</t>
+          <t>Предавам (документ, домашна работа)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Stand out</t>
+          <t>Hand out</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Изпъквам / Откроявам се</t>
+          <t>Раздавам (брошури, листовки)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Stand up for</t>
+          <t>Hang on</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Защитавам (права, някого)</t>
+          <t>Чакам за кратко (на телефон) / Държа се здраво</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Take after</t>
+          <t>Hang out</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Приличам на (баща, майка - роднина)</t>
+          <t>Прекарвам свободното време (вися с приятели)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Take care of</t>
+          <t>Hang up</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Грижа се за / Справям се с</t>
+          <t>Затварям телефона / Закачам дреха</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Take down</t>
+          <t>Hold on</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Записвам / Свалям (нещо окачено)</t>
+          <t>Изчаквам малко / Държа се здраво</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Take off</t>
+          <t>Hold up</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Излитам (за самолет) / Събличам (дрехи) / Тръгвам бързо</t>
+          <t>Забавям (трафик, процес) / Обирам с оръжие</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Take on</t>
+          <t>Keep on</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Наемам (служители) / Поемам отговорност/предизвикателство</t>
+          <t>Продължавам да правя нещо</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Take over</t>
+          <t>Keep up (with)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Поемам контрол / Изкупувам фирма</t>
+          <t>Държа темпото / В крак съм с</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Take up</t>
+          <t>Let down</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Започвам ново хоби/спорт / Заемам пространство</t>
+          <t>Разочаровам някого / Предавам доверие</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Tell off</t>
+          <t>Let in</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Наказвам / Накарвам се на някого (за грешка)</t>
+          <t>Пускам да влезе</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Think over</t>
+          <t>Let out</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Обмислям внимателно</t>
+          <t>Пускам да излезе / Изпускам звук</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Throw away / out</t>
+          <t>Log in / on</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Изхвърлям (нещо ненужно)</t>
+          <t>Влизам в профил (интернет)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Try on</t>
+          <t>Log out / off</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Пробвам (дреха в магазин)</t>
+          <t>Излизам от профил (интернет)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Try out</t>
+          <t>Look after</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Изпробвам (уред, кола)</t>
+          <t>Грижа се за (дете, домашен любимец)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Turn down</t>
+          <t>Look down on</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Намалявам (звук) / Отхвърлям (покана, предложение)</t>
+          <t>Гледам отвисоко / Презирам</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Turn into</t>
+          <t>Look for</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Превръщам се в</t>
+          <t>Търся</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Turn off</t>
+          <t>Look forward to</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Изключвам (уред, осветление) / Завивам по път</t>
+          <t>Очаквам с нетърпение</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Turn on</t>
+          <t>Look into</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Включвам (уред, осветление)</t>
+          <t>Разследвам / Проучвам</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Turn out</t>
+          <t>Look out</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Оказва се, че / Произвеждам</t>
+          <t>Внимавам / Пазя се</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Turn up</t>
+          <t>Look over</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Усилвам (звук) / Появявам се неочаквано</t>
+          <t>Преглеждам бързо</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Use up</t>
+          <t>Look up</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Изразходвам напълно</t>
+          <t>Търся информация (в речник, каталог) / Подобрявам се</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Wake up</t>
+          <t>Look up to</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Събуждам се</t>
+          <t>Уважавам / Възхищавам се на някого</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Warm up</t>
+          <t>Make out</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Загрявам (преди спорт или уред)</t>
+          <t>Разбирам / Разчитам (труден текст) / Справям се</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>Make up</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Измислям си (история) / Гримирам се / Помирявам се</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Make up for</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Компенсирам за</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Mix up</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Обърквам (неща/хора едно с друго)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Pass away</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Почивам (умирам - учтиво)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Pass out</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Припадам / Губя съзнание</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Pay back</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Връщам заем (на някого)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Pay off</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Изплащам напълно дълг / Давам добър резултат (усилие)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Pick up</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Вдигам / Взимам някого с кола / Уча лесно</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Point out</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Посочвам / Обръщам внимание на</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Pull over</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Спирам край пътя (за превозно средство)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Put away</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Прибирам на мястото му / Спестявам пари</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Put off</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Отлагам (среща, ангажимент) / Отблъсквам (някого)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Put on</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Обличам (дреха) / Обувам / Надебелявам / Включвам</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Put out</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Гася (пожар, цигара) / Безпокоя (някого)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Put up with</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Измъчвам се / Толерирам / Търпя (неприятно нещо)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Run into</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Сблъсквам се / Срещам случайно някого</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Run out of</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Свършвам (напр. нямаме бензин, мляко)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Run over</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Прегазвам с кола / Преглеждам бързо</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Save up</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Спестявам (пари за нещо специално)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>See off</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Изпращам някого (на гара, летище)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Set off / out</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Тръгвам на път / Задействам аларма</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Set up</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Основавам (фирма) / Организирам / Нагласям капан</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Show off</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Фукам се / Перча се</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Show up</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Появявам се / Идвам на среща</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Slow down</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Намалявам скоростта</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Sort out</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Решавам проблем / Подреждам</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Stand by</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Подкрепям (някого) / Изчаквам готовност</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Stand out</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Изпъквам / Откроявам се</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Stand up for</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Защитавам (права, някого)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Take after</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Приличам на (баща, майка - роднина)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Take care of</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Грижа се за / Справям се с</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Take down</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Записвам / Свалям (нещо окачено)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Take off</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Излитам (за самолет) / Събличам (дрехи) / Тръгвам бързо</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Take on</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Наемам (служители) / Поемам отговорност/предизвикателство</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Take over</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Поемам контрол / Изкупувам фирма</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Take up</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Започвам ново хоби/спорт / Заемам пространство</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Tell off</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Наказвам / Накарвам се на някого (за грешка)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Think over</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Обмислям внимателно</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Throw away / out</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Изхвърлям (нещо ненужно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Try on</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Пробвам (дреха в магазин)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Try out</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Изпробвам (уред, кола)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Turn down</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Намалявам (звук) / Отхвърлям (покана, предложение)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Turn into</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Превръщам се в</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Turn off</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Изключвам (уред, осветление) / Завивам по път</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Turn on</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Включвам (уред, осветление)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Turn out</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Оказва се, че / Произвеждам</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Turn up</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Усилвам (звук) / Появявам се неочаквано</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Use up</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Изразходвам напълно</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Wake up</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Събуждам се</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Warm up</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Загрявам (преди спорт или уред)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
           <t>Work out</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>Тренирам във фитнес / Решавам (проблем) / Намирам изход</t>
         </is>
